--- a/ig/test-tabs-svs/ValueSet-jdv-j408-orientation-ms.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j408-orientation-ms.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="78">
   <si>
     <t>Property</t>
   </si>
@@ -176,9 +176,6 @@
   </si>
   <si>
     <t>warning-draft</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j408-orientation-ms|20260601120000</t>
   </si>
   <si>
     <t>Level</t>
@@ -677,7 +674,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -741,14 +738,6 @@
         <v>52</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s" s="2">
         <v>51</v>
       </c>
     </row>
@@ -764,36 +753,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>53</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>54</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>55</v>
       </c>
       <c r="C1" t="s" s="1">
         <v>49</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>55</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>58</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>40</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s" s="2">
         <v>36</v>
@@ -810,13 +799,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s" s="2">
         <v>40</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s" s="2">
         <v>38</v>
@@ -833,13 +822,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>45</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>41</v>
@@ -856,13 +845,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>45</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>43</v>
@@ -879,19 +868,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C6" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="D6" t="s" s="2">
+      <c r="E6" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="E6" t="s" s="2">
-        <v>65</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>15</v>
@@ -902,19 +891,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="E7" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>67</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>15</v>
@@ -925,19 +914,19 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>15</v>
@@ -948,19 +937,19 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E9" t="s" s="2">
         <v>69</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>70</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>15</v>
@@ -971,19 +960,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>71</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>72</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>15</v>
@@ -994,19 +983,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>74</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>15</v>
@@ -1017,19 +1006,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>75</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>76</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>15</v>
@@ -1040,19 +1029,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E13" t="s" s="2">
         <v>77</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>15</v>
